--- a/data/trans_dic/DCD_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,8</t>
+          <t>6,77; 11,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,56; 24,19</t>
+          <t>17,34; 24,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,57</t>
+          <t>12,49; 16,71</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,44</t>
+          <t>8,19; 13,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,14; 27,11</t>
+          <t>20,54; 27,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 19,12</t>
+          <t>14,46; 18,79</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 16,91</t>
+          <t>3,94; 17,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,43; 40,39</t>
+          <t>28,17; 39,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 21,99</t>
+          <t>7,12; 21,75</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 20,81</t>
+          <t>15,92; 20,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 26,07</t>
+          <t>11,47; 26,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 21,75</t>
+          <t>13,06; 21,58</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 23,63</t>
+          <t>16,41; 23,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,3; 37,28</t>
+          <t>24,8; 37,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 30,81</t>
+          <t>22,67; 30,81</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,62</t>
+          <t>1,39; 6,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,42; 32,42</t>
+          <t>26,8; 32,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,54; 25,58</t>
+          <t>20,52; 25,88</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,2; 14,86</t>
+          <t>10,44; 14,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,08; 28,36</t>
+          <t>21,15; 28,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,4; 21,48</t>
+          <t>17,2; 21,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34171; 59596</t>
+          <t>34205; 58185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78578; 108255</t>
+          <t>77581; 107798</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118285; 157907</t>
+          <t>118969; 159229</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35322; 60788</t>
+          <t>37031; 60943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77043; 103705</t>
+          <t>78572; 105418</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120761; 159625</t>
+          <t>120695; 156827</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25443; 113005</t>
+          <t>26314; 115162</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47449; 67421</t>
+          <t>47020; 66362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54359; 183628</t>
+          <t>59489; 181672</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>166792; 215332</t>
+          <t>164782; 213266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102595; 255021</t>
+          <t>112161; 254349</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>273356; 437789</t>
+          <t>262870; 434434</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77506; 112247</t>
+          <t>77943; 111379</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>196013; 313675</t>
+          <t>208668; 314355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>302004; 405576</t>
+          <t>298382; 405512</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3422; 15914</t>
+          <t>3341; 16407</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>201137; 246847</t>
+          <t>204010; 247749</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>205766; 256290</t>
+          <t>205605; 259288</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>344292; 501579</t>
+          <t>352556; 499834</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>754247; 1014569</t>
+          <t>756796; 1012035</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1209785; 1493355</t>
+          <t>1195890; 1485211</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/DCD_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 11,52</t>
+          <t>6,82; 11,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 24,09</t>
+          <t>17,91; 24,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 16,71</t>
+          <t>12,81; 16,9</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,48</t>
+          <t>7,6; 12,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 27,55</t>
+          <t>21,37; 28,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,79</t>
+          <t>14,76; 19,36</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 17,23</t>
+          <t>12,67; 19,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,17; 39,76</t>
+          <t>28,65; 40,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 21,75</t>
+          <t>18,44; 24,18</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 20,61</t>
+          <t>15,63; 20,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 26,0</t>
+          <t>22,86; 28,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 21,58</t>
+          <t>19,35; 22,89</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,41; 23,45</t>
+          <t>14,42; 20,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,8; 37,36</t>
+          <t>33,28; 38,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,67; 30,81</t>
+          <t>26,19; 30,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,82</t>
+          <t>1,38; 6,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,8; 32,54</t>
+          <t>26,05; 31,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,52; 25,88</t>
+          <t>20,61; 25,57</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 14,81</t>
+          <t>12,91; 15,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 28,29</t>
+          <t>27,08; 29,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,2; 21,36</t>
+          <t>20,5; 22,27</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45773</t>
+          <t>50333</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>102855</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138053</t>
+          <t>153188</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34205; 58185</t>
+          <t>37572; 64784</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77581; 107798</t>
+          <t>87458; 119771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118969; 159229</t>
+          <t>133103; 175631</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>49106</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138079</t>
+          <t>152786</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37031; 60943</t>
+          <t>36741; 62450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78572; 105418</t>
+          <t>90409; 119976</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>120695; 156827</t>
+          <t>133756; 175510</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>75354</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>64002</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125429</t>
+          <t>139356</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26314; 115162</t>
+          <t>59754; 92789</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47020; 66362</t>
+          <t>53714; 75262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59489; 181672</t>
+          <t>121538; 159368</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>188212</t>
+          <t>201474</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>194198</t>
+          <t>218712</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382410</t>
+          <t>420186</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>164782; 213266</t>
+          <t>176933; 230614</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>112161; 254349</t>
+          <t>196837; 241942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>262870; 434434</t>
+          <t>385679; 456282</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93487</t>
+          <t>99197</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>273279</t>
+          <t>296636</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366766</t>
+          <t>395833</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77943; 111379</t>
+          <t>81914; 118728</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>208668; 314355</t>
+          <t>276533; 321287</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>298382; 405512</t>
+          <t>366307; 426930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>223551</t>
+          <t>242976</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231382</t>
+          <t>250522</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3341; 16407</t>
+          <t>3271; 14991</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>204010; 247749</t>
+          <t>219902; 267715</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>205605; 259288</t>
+          <t>222928; 276547</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>451137</t>
+          <t>483010</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>930982</t>
+          <t>1028860</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1382119</t>
+          <t>1511870</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>352556; 499834</t>
+          <t>444586; 524676</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>756796; 1012035</t>
+          <t>984546; 1075406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1195890; 1485211</t>
+          <t>1451080; 1576095</t>
         </is>
       </c>
     </row>
